--- a/dev/StructureDefinition-bc-practitioner-condition-extension.xlsx
+++ b/dev/StructureDefinition-bc-practitioner-condition-extension.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-06-23T20:38:35+00:00</t>
+    <t>2026-01-23T00:06:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1283,7 +1283,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="5" hidden="true">
+    <row r="5">
       <c r="A5" t="s" s="2">
         <v>97</v>
       </c>
@@ -1699,7 +1699,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="9" hidden="true">
+    <row r="9">
       <c r="A9" t="s" s="2">
         <v>112</v>
       </c>
@@ -1802,7 +1802,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="10" hidden="true">
+    <row r="10">
       <c r="A10" t="s" s="2">
         <v>119</v>
       </c>
@@ -2218,7 +2218,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="14" hidden="true">
+    <row r="14">
       <c r="A14" t="s" s="2">
         <v>124</v>
       </c>
@@ -2321,7 +2321,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="15" hidden="true">
+    <row r="15">
       <c r="A15" t="s" s="2">
         <v>126</v>
       </c>
@@ -2737,7 +2737,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="19" hidden="true">
+    <row r="19">
       <c r="A19" t="s" s="2">
         <v>131</v>
       </c>
@@ -2840,7 +2840,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="20" hidden="true">
+    <row r="20">
       <c r="A20" t="s" s="2">
         <v>132</v>
       </c>
@@ -3256,7 +3256,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="24" hidden="true">
+    <row r="24">
       <c r="A24" t="s" s="2">
         <v>137</v>
       </c>
@@ -3359,7 +3359,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="25" hidden="true">
+    <row r="25">
       <c r="A25" t="s" s="2">
         <v>139</v>
       </c>
@@ -3464,7 +3464,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="26" hidden="true">
+    <row r="26">
       <c r="A26" t="s" s="2">
         <v>144</v>
       </c>
@@ -3569,7 +3569,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="27" hidden="true">
+    <row r="27">
       <c r="A27" t="s" s="2">
         <v>149</v>
       </c>
@@ -3884,12 +3884,12 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:AK29">
-    <filterColumn colId="6">
+    <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
       </customFilters>
     </filterColumn>
-    <filterColumn colId="26">
+    <filterColumn colId="27">
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
